--- a/output/laminas_comunales/comunal_s_fonasa_a_2022_biobio.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2022_biobio.xlsx
@@ -375,256 +375,256 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="C2">
-        <v>193452</v>
+        <v>94.28724877745428</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="C3">
-        <v>172248</v>
+        <v>93.8209675726729</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Talcahuano</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="C4">
-        <v>126921</v>
+        <v>93.6828562238662</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="C5">
-        <v>113254</v>
+        <v>92.96351960650362</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="C6">
-        <v>101556</v>
+        <v>92.9557753312185</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hualpén</t>
+          <t>Contulmo</t>
         </is>
       </c>
       <c r="C7">
-        <v>79661</v>
+        <v>92.81999422132331</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
+          <t>Quilaco</t>
         </is>
       </c>
       <c r="C8">
-        <v>71152</v>
+        <v>92.7655876602216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tomé</t>
+          <t>Santa Juana</t>
         </is>
       </c>
       <c r="C9">
-        <v>53171</v>
+        <v>92.74935369446281</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="C10">
-        <v>45328</v>
+        <v>92.68172078457228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Quilleco</t>
         </is>
       </c>
       <c r="C11">
-        <v>44701</v>
+        <v>92.41610738255034</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Los Alamos</t>
         </is>
       </c>
       <c r="C12">
-        <v>35021</v>
+        <v>92.34891216760677</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Tirúa</t>
         </is>
       </c>
       <c r="C13">
-        <v>34020</v>
+        <v>92.2847100175747</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Alto Biobío</t>
         </is>
       </c>
       <c r="C14">
-        <v>33356</v>
+        <v>92.25227674323773</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cabrero</t>
+          <t>Hualqui</t>
         </is>
       </c>
       <c r="C15">
-        <v>30044</v>
+        <v>91.91342306293197</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>Tucapel</t>
         </is>
       </c>
       <c r="C16">
-        <v>29889</v>
+        <v>91.83138009445513</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hualqui</t>
+          <t>Cabrero</t>
         </is>
       </c>
       <c r="C17">
-        <v>25267</v>
+        <v>91.56127144729223</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C18">
-        <v>25218</v>
+        <v>91.27369956246962</v>
       </c>
     </row>
     <row r="19">
@@ -639,232 +639,232 @@
         </is>
       </c>
       <c r="C19">
-        <v>25086</v>
+        <v>91.21186779624041</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Los Alamos</t>
+          <t>San Rosendo</t>
         </is>
       </c>
       <c r="C20">
-        <v>22921</v>
+        <v>91.05236400610066</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Laja</t>
+          <t>Antuco</t>
         </is>
       </c>
       <c r="C21">
-        <v>22586</v>
+        <v>90.73724007561437</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yumbel</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="C22">
-        <v>21712</v>
+        <v>90.41802388707926</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tucapel</t>
+          <t>Nacimiento</t>
         </is>
       </c>
       <c r="C23">
-        <v>15750</v>
+        <v>89.98073217726397</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="C24">
-        <v>15427</v>
+        <v>89.79042034784676</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Yumbel</t>
         </is>
       </c>
       <c r="C25">
-        <v>14563</v>
+        <v>89.52663697839354</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Arauco</t>
         </is>
       </c>
       <c r="C26">
-        <v>11265</v>
+        <v>89.31877885179424</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Negrete</t>
+          <t>Laja</t>
         </is>
       </c>
       <c r="C27">
-        <v>11246</v>
+        <v>89.13532499309365</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tirúa</t>
+          <t>Tomé</t>
         </is>
       </c>
       <c r="C28">
-        <v>10502</v>
+        <v>88.48265992145377</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Quilleco</t>
+          <t>Hualpén</t>
         </is>
       </c>
       <c r="C29">
-        <v>9639</v>
+        <v>85.99263793084836</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Alto Biobío</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C30">
-        <v>6787</v>
+        <v>85.65925283055628</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Contulmo</t>
+          <t>Talcahuano</t>
         </is>
       </c>
       <c r="C31">
-        <v>6425</v>
+        <v>80.91252183447871</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Antuco</t>
+          <t>Chiguayante</t>
         </is>
       </c>
       <c r="C32">
-        <v>4320</v>
+        <v>79.38413477630257</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Quilaco</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="C33">
-        <v>4270</v>
+        <v>74.77794274699799</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
+          <t>San Pedro de la Paz</t>
         </is>
       </c>
       <c r="C34">
-        <v>3582</v>
+        <v>73.48001939092245</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +920,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
